--- a/demo/asteria/sources/finance/payment_runs.xlsx
+++ b/demo/asteria/sources/finance/payment_runs.xlsx
@@ -55,23 +55,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PR-RUN-202605</t>
+          <t>PR-RUN-202602</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>412885.4</v>
+        <v>0.0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -93,23 +93,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PR-RUN-202606</t>
+          <t>PR-RUN-202603</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3">
-        <v>366120.15</v>
+        <v>576642.91</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -119,7 +119,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>finance.manager@asteria.invalid</t>
+          <t>cfo@asteria.invalid</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -131,36 +131,188 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>PR-RUN-202604</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>46</v>
+      </c>
+      <c r="D4">
+        <v>1220452.11</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ap.clerk@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PR-RUN-202605</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>1209276.33</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ap.clerk@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PR-RUN-202606</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>52</v>
+      </c>
+      <c r="D6">
+        <v>1127566.44</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ap.clerk@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>PR-RUN-202607</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C4">
-        <v>33</v>
-      </c>
-      <c r="D4">
-        <v>448902.6</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ap.clerk@asteria.invalid</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>cfo@asteria.invalid</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="C7">
+        <v>55</v>
+      </c>
+      <c r="D7">
+        <v>1242724.54</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ap.clerk@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PR-RUN-202608</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>1807255.33</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ap.clerk@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>cfo@asteria.invalid</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
